--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486310_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486310_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4426</v>
+        <v>7.0961</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3551</v>
+        <v>8.162699999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.9125</v>
+        <v>-1.0666</v>
       </c>
       <c r="G2" t="n">
         <v>7.52</v>
@@ -610,13 +610,13 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5123</v>
+        <v>-0.8589</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9469</v>
+        <v>-0.1394</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5654</v>
+        <v>-0.7195</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7717</v>
+        <v>5.9588</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4895</v>
+        <v>4.7383</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2822</v>
+        <v>1.2205</v>
       </c>
       <c r="G3" t="n">
         <v>3.0677</v>
@@ -688,13 +688,13 @@
         <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8186</v>
+        <v>-0.6315</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4638</v>
+        <v>-0.2151</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3548</v>
+        <v>-0.4164</v>
       </c>
       <c r="V3" t="n">
         <v>1.13</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ RAMOS</t>
+          <t>J. YU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0778</v>
+        <v>0.6427</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0101</v>
+        <v>-0.4412</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0676</v>
+        <v>1.0839</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1298</v>
+        <v>1.9375</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1282</v>
+        <v>1.0977</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0016</v>
+        <v>0.8399</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8952</v>
+        <v>0.9527</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4745</v>
+        <v>0.073</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4207</v>
+        <v>0.8797</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.025</v>
+        <v>0.9848</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6027</v>
+        <v>1.0247</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4224</v>
+        <v>-0.0399</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7401</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>2.8276</v>
+        <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1627</v>
+        <v>-1.2948</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0072</v>
+        <v>-0.3064</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1699</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3698</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. YU</t>
+          <t>S. RODRÍGUEZ RAMOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8363</v>
+        <v>0.448</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.1881</v>
       </c>
       <c r="F5" t="n">
-        <v>0.899</v>
+        <v>0.6361</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9375</v>
+        <v>-0.1298</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0977</v>
+        <v>-0.1282</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8399</v>
+        <v>-0.0016</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9527</v>
+        <v>0.8952</v>
       </c>
       <c r="K5" t="n">
-        <v>0.073</v>
+        <v>0.4745</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8797</v>
+        <v>0.4207</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9848</v>
+        <v>-1.025</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0247</v>
+        <v>-0.6027</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0399</v>
+        <v>-0.4224</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0875</v>
+        <v>2.8276</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1012</v>
+        <v>-0.7925</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0721</v>
+        <v>-0.1911</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1733</v>
+        <v>-0.6015</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4113</v>
+        <v>-0.1193</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8855</v>
+        <v>-0.5935</v>
       </c>
       <c r="F6" t="n">
         <v>0.4742</v>
@@ -922,10 +922,10 @@
         <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.8326</v>
+        <v>-1.5406</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7294</v>
+        <v>-0.4374</v>
       </c>
       <c r="U6" t="n">
         <v>-1.1032</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. KANDE KIELI</t>
+          <t>R. JOHNSON JR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5684</v>
+        <v>-2.2784</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8974</v>
+        <v>-1.0767</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.4658</v>
+        <v>-1.2017</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.3364</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.8902</v>
+        <v>-1.4441</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5538</v>
+        <v>1.3523</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.0381</v>
+        <v>0.3124</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.2294</v>
+        <v>-0.3793</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1912</v>
+        <v>0.6917</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2983</v>
+        <v>-0.4042</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6608</v>
+        <v>-1.0648</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3626</v>
+        <v>0.6606</v>
       </c>
       <c r="P7" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8534</v>
+        <v>-0.5792</v>
       </c>
       <c r="T7" t="n">
-        <v>2.0453</v>
+        <v>-0.3016</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1919</v>
+        <v>-0.2776</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3904</v>
+        <v>-2.2599</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8902</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.2806</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. TABOADA HEISKANEN</t>
+          <t>G. KANDE KIELI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.5287</v>
+        <v>-2.7918</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3219</v>
+        <v>-0.4185</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2068</v>
+        <v>-2.3733</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1659</v>
+        <v>-4.3364</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7785</v>
+        <v>-4.8902</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3873</v>
+        <v>0.5538</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.1969</v>
+        <v>-3.0381</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7451</v>
+        <v>-3.2294</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.4519</v>
+        <v>0.1912</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0311</v>
+        <v>-1.2983</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0335</v>
+        <v>-1.6608</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0645</v>
+        <v>0.3626</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.305</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2329</v>
+        <v>0.63</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.125</v>
+        <v>0.7294</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1079</v>
+        <v>-0.0994</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.13</v>
+        <v>-0.3904</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.8902</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.13</v>
+        <v>-2.2806</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. JOHNSON JR</t>
+          <t>C. TABOADA HEISKANEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5676</v>
+        <v>-3.2868</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.996</v>
+        <v>-2.1416</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5716</v>
+        <v>-1.1452</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-2.1659</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4441</v>
+        <v>-0.7785</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3523</v>
+        <v>-1.3873</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3124</v>
+        <v>-2.1969</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3793</v>
+        <v>-0.7451</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6917</v>
+        <v>-1.4519</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4042</v>
+        <v>0.0311</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0648</v>
+        <v>-0.0335</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6606</v>
+        <v>0.0645</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6525</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7401</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.8684</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2209</v>
+        <v>0.0553</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6475</v>
+        <v>-0.0463</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.2599</v>
+        <v>-1.13</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.2599</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9179</v>
+        <v>-3.5073</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.7803</v>
+        <v>-4.3081</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8624000000000001</v>
+        <v>0.8008</v>
       </c>
       <c r="G10" t="n">
         <v>-2.258</v>
@@ -1234,13 +1234,13 @@
         <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0722</v>
+        <v>-0.6615</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7174</v>
+        <v>-0.2451</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3548</v>
+        <v>-0.4164</v>
       </c>
       <c r="V10" t="n">
         <v>0.9347</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.134499999999999</v>
+        <v>2.162</v>
       </c>
       <c r="E11" t="n">
-        <v>2.705699999999999</v>
+        <v>3.7333</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5713</v>
+        <v>-1.571300000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>3.442099999999999</v>
+        <v>3.442100000000001</v>
       </c>
       <c r="H11" t="n">
         <v>-4.7296</v>
@@ -1291,7 +1291,7 @@
         <v>-1.549</v>
       </c>
       <c r="L11" t="n">
-        <v>8.470599999999997</v>
+        <v>8.470599999999999</v>
       </c>
       <c r="M11" t="n">
         <v>-3.4798</v>
@@ -1312,10 +1312,10 @@
         <v>14.1379</v>
       </c>
       <c r="S11" t="n">
-        <v>-6.7475</v>
+        <v>-5.720000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.0788</v>
+        <v>-1.0514</v>
       </c>
       <c r="U11" t="n">
         <v>-4.6687</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.1228</v>
+        <v>5.5205</v>
       </c>
       <c r="E12" t="n">
-        <v>4.029</v>
+        <v>4.1408</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0938</v>
+        <v>1.3797</v>
       </c>
       <c r="G12" t="n">
         <v>1.2927</v>
@@ -1390,13 +1390,13 @@
         <v>1.0875</v>
       </c>
       <c r="S12" t="n">
-        <v>1.81</v>
+        <v>1.2077</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2091</v>
+        <v>0.3209</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6009</v>
+        <v>0.8868</v>
       </c>
       <c r="V12" t="n">
         <v>3.0202</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2951</v>
+        <v>3.7261</v>
       </c>
       <c r="E13" t="n">
-        <v>4.013</v>
+        <v>3.4542</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2821</v>
+        <v>0.2719</v>
       </c>
       <c r="G13" t="n">
         <v>0.7725</v>
@@ -1468,13 +1468,13 @@
         <v>0.435</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9576</v>
+        <v>1.3886</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3207</v>
+        <v>0.7619</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6369</v>
+        <v>0.6267</v>
       </c>
       <c r="V13" t="n">
         <v>1.13</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1964</v>
+        <v>1.1643</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8569</v>
+        <v>1.5216</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6605</v>
+        <v>-0.3574</v>
       </c>
       <c r="G14" t="n">
         <v>-0.5759</v>
@@ -1546,13 +1546,13 @@
         <v>0.435</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2948</v>
+        <v>1.2627</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1152</v>
+        <v>0.7799</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1796</v>
+        <v>0.4828</v>
       </c>
       <c r="V14" t="n">
         <v>1.13</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9472</v>
+        <v>1.0153</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3251</v>
+        <v>3.2134</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.3779</v>
+        <v>-2.1981</v>
       </c>
       <c r="G15" t="n">
         <v>2.4879</v>
@@ -1624,13 +1624,13 @@
         <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5241</v>
+        <v>0.5921</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4951</v>
+        <v>0.3833</v>
       </c>
       <c r="U15" t="n">
-        <v>0.029</v>
+        <v>0.2088</v>
       </c>
       <c r="V15" t="n">
         <v>-2.0647</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0531</v>
+        <v>0.1576</v>
       </c>
       <c r="E16" t="n">
         <v>-0.0622</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0091</v>
+        <v>0.2198</v>
       </c>
       <c r="G16" t="n">
         <v>0.0548</v>
@@ -1702,13 +1702,13 @@
         <v>0.2175</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3254</v>
+        <v>-0.1148</v>
       </c>
       <c r="T16" t="n">
         <v>-0.137</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1884</v>
+        <v>0.0222</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.3053</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3503</v>
+        <v>-0.462</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2852</v>
+        <v>0.1568</v>
       </c>
       <c r="G17" t="n">
         <v>1.2909</v>
@@ -1780,13 +1780,13 @@
         <v>0.2175</v>
       </c>
       <c r="S17" t="n">
-        <v>1.209</v>
+        <v>0.9689</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5516</v>
+        <v>0.4398</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6574</v>
+        <v>0.529</v>
       </c>
       <c r="V17" t="n">
         <v>-1.695</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0747</v>
+        <v>-0.8948</v>
       </c>
       <c r="E18" t="n">
         <v>-0.926</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1486</v>
+        <v>0.0312</v>
       </c>
       <c r="G18" t="n">
         <v>-0.888</v>
@@ -1858,13 +1858,13 @@
         <v>0.2175</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.209</v>
+        <v>-0.0291</v>
       </c>
       <c r="T18" t="n">
         <v>-0.274</v>
       </c>
       <c r="U18" t="n">
-        <v>0.065</v>
+        <v>0.2448</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1952</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2757</v>
+        <v>-1.1865</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0248</v>
+        <v>-1.5777</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2509</v>
+        <v>0.3913</v>
       </c>
       <c r="G19" t="n">
         <v>-1.8782</v>
@@ -1936,13 +1936,13 @@
         <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0702</v>
+        <v>1.019</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5071</v>
+        <v>0.9542</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5773</v>
+        <v>0.0649</v>
       </c>
       <c r="V19" t="n">
         <v>0.7602</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.414</v>
+        <v>-2.0774</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2195</v>
+        <v>-1.9959</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1945</v>
+        <v>-0.0815</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1671</v>
@@ -2014,13 +2014,13 @@
         <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7107</v>
+        <v>1.0473</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3701</v>
+        <v>0.5936</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3405</v>
+        <v>0.4536</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1399</v>
+        <v>-2.7842</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4198</v>
+        <v>-2.9786</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7201</v>
+        <v>0.1943</v>
       </c>
       <c r="G21" t="n">
         <v>-2.6464</v>
@@ -2092,13 +2092,13 @@
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7691</v>
+        <v>1.1248</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1152</v>
+        <v>0.5564</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3461</v>
+        <v>0.5684</v>
       </c>
       <c r="V21" t="n">
         <v>1.13</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6735</v>
+        <v>-3.2348</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.6501</v>
+        <v>-2.756</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0234</v>
+        <v>-0.4788</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1853</v>
@@ -2170,13 +2170,13 @@
         <v>0.6525</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9231</v>
+        <v>0.5155</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6044</v>
+        <v>0.2896</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3187</v>
+        <v>0.2259</v>
       </c>
       <c r="V22" t="n">
         <v>-1.13</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.134500000000001</v>
+        <v>1.100800000000003</v>
       </c>
       <c r="E23" t="n">
-        <v>1.571299999999999</v>
+        <v>1.5716</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7057</v>
+        <v>-0.4708000000000004</v>
       </c>
       <c r="G23" t="n">
         <v>-3.4421</v>
@@ -2248,13 +2248,13 @@
         <v>7.6125</v>
       </c>
       <c r="S23" t="n">
-        <v>6.7476</v>
+        <v>8.982699999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>4.6687</v>
+        <v>4.6686</v>
       </c>
       <c r="U23" t="n">
-        <v>2.0788</v>
+        <v>4.313899999999999</v>
       </c>
       <c r="V23" t="n">
         <v>2.0855</v>
